--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513665_FASEFINALBFFB4_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513665_FASEFINALBFFB4_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5071</v>
+        <v>1.9773</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5746</v>
+        <v>3.329</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0675</v>
+        <v>-1.3517</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6232</v>
+        <v>3.2677</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7108</v>
+        <v>4.0395</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9124</v>
+        <v>-0.7718</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2967</v>
+        <v>4.5702</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4081</v>
+        <v>3.9539</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8887</v>
+        <v>0.6163</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6735</v>
+        <v>-1.3024</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3027</v>
+        <v>0.0856</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9762</v>
+        <v>-1.3881</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1947</v>
+        <v>0.9737</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9474</v>
+        <v>-0.9737</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7526</v>
+        <v>1.9474</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0786</v>
+        <v>0.2296</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0042</v>
+        <v>-0.2159</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0745</v>
+        <v>0.4455</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-2.4937</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2211</v>
+        <v>-0.0516</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2211</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0737</v>
+        <v>1.8288</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1346</v>
+        <v>1.7015</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9391</v>
+        <v>0.1273</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2568</v>
+        <v>1.6232</v>
       </c>
       <c r="H3" t="n">
-        <v>1.17</v>
+        <v>0.7108</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4268</v>
+        <v>0.9124</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4891</v>
+        <v>2.2967</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0726</v>
+        <v>0.4081</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5835</v>
+        <v>1.8887</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7459</v>
+        <v>-0.6735</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0974</v>
+        <v>0.3027</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8433</v>
+        <v>-0.9762</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9737</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9737</v>
+        <v>-1.9474</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9474</v>
+        <v>1.7526</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2984</v>
+        <v>0.4003</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3397</v>
+        <v>0.1311</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9587</v>
+        <v>0.2692</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9416</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2795</v>
+        <v>1.2211</v>
       </c>
       <c r="X3" t="n">
         <v>-1.2211</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6999</v>
+        <v>0.5644</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2464</v>
+        <v>-0.0408</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5465</v>
+        <v>0.6052</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2677</v>
+        <v>-0.2568</v>
       </c>
       <c r="H4" t="n">
-        <v>4.0395</v>
+        <v>1.17</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7718</v>
+        <v>-1.4268</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5702</v>
+        <v>0.4891</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9539</v>
+        <v>1.0726</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6163</v>
+        <v>-0.5835</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3024</v>
+        <v>-0.7459</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0856</v>
+        <v>0.0974</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3881</v>
+        <v>-0.8433</v>
       </c>
       <c r="P4" t="n">
         <v>0.9737</v>
@@ -766,22 +766,22 @@
         <v>1.9474</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0478</v>
+        <v>0.7891</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2985</v>
+        <v>0.1643</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2507</v>
+        <v>0.6248</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.4937</v>
+        <v>-0.9416</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0516</v>
+        <v>0.2795</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4421</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8300999999999999</v>
+        <v>-0.0951</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8497</v>
+        <v>-0.3652</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0196</v>
+        <v>0.27</v>
       </c>
       <c r="G5" t="n">
         <v>-1.2892</v>
@@ -844,13 +844,13 @@
         <v>1.9474</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3988</v>
+        <v>0.3362</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5104</v>
+        <v>-0.0258</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1116</v>
+        <v>0.362</v>
       </c>
       <c r="V5" t="n">
         <v>1.8316</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1034</v>
+        <v>-0.6251</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1116</v>
+        <v>-0.6889</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0638</v>
       </c>
       <c r="G6" t="n">
         <v>-2.16</v>
@@ -922,13 +922,13 @@
         <v>0.9737</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.476</v>
+        <v>0.0023</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4236</v>
+        <v>-0.0009</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0524</v>
+        <v>0.0032</v>
       </c>
       <c r="V6" t="n">
         <v>0.5590000000000001</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. VINALLONGA BLANCO</t>
+          <t>A. VALLE VIVES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5111</v>
+        <v>-1.1813</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.828</v>
+        <v>-1.2586</v>
       </c>
       <c r="F7" t="n">
-        <v>0.317</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3426</v>
+        <v>-1.9471</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4679</v>
+        <v>-1.5287</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8105</v>
+        <v>-0.4184</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3823</v>
+        <v>-0.8774</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0468</v>
+        <v>-0.8774</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6645</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7249</v>
+        <v>-1.0696</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5789</v>
+        <v>-0.6513</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.146</v>
+        <v>-0.4184</v>
       </c>
       <c r="P7" t="n">
+        <v>-0.9737</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-2.1421</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-3.1158</v>
-      </c>
       <c r="R7" t="n">
-        <v>0.9737</v>
+        <v>1.1684</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9736</v>
+        <v>0.5185</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9054</v>
+        <v>0.5399</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0682</v>
+        <v>-0.0215</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7139</v>
+        <v>-1.3924</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8824</v>
+        <v>-2.4218</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1685</v>
+        <v>1.0294</v>
       </c>
       <c r="G8" t="n">
         <v>0.4479</v>
@@ -1078,13 +1078,13 @@
         <v>0.9737</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2598</v>
+        <v>0.5812</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5473</v>
+        <v>-0.0867</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8071</v>
+        <v>0.6679</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2795</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VALLE VIVES</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9719</v>
+        <v>-1.7521</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7431</v>
+        <v>-2.0412</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2288</v>
+        <v>0.2891</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9471</v>
+        <v>-0.3426</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5287</v>
+        <v>0.4679</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4184</v>
+        <v>-0.8105</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8774</v>
+        <v>0.3823</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8774</v>
+        <v>1.0468</v>
       </c>
       <c r="L9" t="n">
+        <v>-0.6645</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.7249</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.5789</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.146</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-2.1421</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-3.1158</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.9737</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.7326</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.6922</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="V9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
-        <v>-1.0696</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-0.6513</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-0.4184</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.9737</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-2.1421</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.1684</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.2722</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.0554</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.3275</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.2211</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4058</v>
+        <v>-3.1978</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4761</v>
+        <v>-0.8508</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9297</v>
+        <v>-2.3471</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4882</v>
@@ -1234,13 +1234,13 @@
         <v>0.9737</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5177</v>
+        <v>0.7256</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7817</v>
+        <v>0.407</v>
       </c>
       <c r="U10" t="n">
-        <v>0.736</v>
+        <v>0.3186</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2142</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2369</v>
+        <v>-4.073</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5807</v>
+        <v>-5.3333</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3438</v>
+        <v>1.2603</v>
       </c>
       <c r="G11" t="n">
         <v>-5.2431</v>
@@ -1312,13 +1312,13 @@
         <v>1.9474</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3431</v>
+        <v>0.5069</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3397</v>
+        <v>0.587</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0034</v>
+        <v>-0.0801</v>
       </c>
       <c r="V11" t="n">
         <v>1.8316</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.4924</v>
+        <v>-7.946300000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.516000000000002</v>
+        <v>-7.9701</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0237000000000005</v>
+        <v>0.02360000000000007</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.388200000000001</v>
+        <v>-8.388199999999999</v>
       </c>
       <c r="H12" t="n">
         <v>3.138</v>
@@ -1366,13 +1366,13 @@
         <v>0.3277999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>4.880900000000001</v>
+        <v>4.8809</v>
       </c>
       <c r="L12" t="n">
         <v>-4.553</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.715800000000002</v>
+        <v>-8.7158</v>
       </c>
       <c r="N12" t="n">
         <v>-1.7428</v>
@@ -1390,13 +1390,13 @@
         <v>14.6054</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2764</v>
+        <v>4.8223</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6463000000000001</v>
+        <v>2.1922</v>
       </c>
       <c r="U12" t="n">
-        <v>2.6303</v>
+        <v>2.63</v>
       </c>
       <c r="V12" t="n">
         <v>-0.4857000000000005</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.5036</v>
+        <v>8.991199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>9.9863</v>
+        <v>10.2853</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4827</v>
+        <v>-1.2941</v>
       </c>
       <c r="G13" t="n">
         <v>5.8963</v>
@@ -1468,13 +1468,13 @@
         <v>2.1421</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2827</v>
+        <v>-0.7951</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7236</v>
+        <v>-0.4245</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5591</v>
+        <v>-0.3706</v>
       </c>
       <c r="V13" t="n">
         <v>2.7216</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7984</v>
+        <v>2.7157</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4122</v>
+        <v>2.1132</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3861</v>
+        <v>0.6025</v>
       </c>
       <c r="G14" t="n">
         <v>0.3095</v>
@@ -1546,13 +1546,13 @@
         <v>2.921</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1206</v>
+        <v>-0.2033</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0489</v>
+        <v>-0.2501</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1696</v>
+        <v>0.0468</v>
       </c>
       <c r="V14" t="n">
         <v>0.6621</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5689</v>
+        <v>1.402</v>
       </c>
       <c r="E15" t="n">
         <v>0.4672</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1018</v>
+        <v>0.9348</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1698</v>
@@ -1624,13 +1624,13 @@
         <v>2.1421</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2071</v>
+        <v>0.0401</v>
       </c>
       <c r="T15" t="n">
         <v>-0.3775</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5846</v>
+        <v>0.4176</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6105</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2388</v>
+        <v>1.2836</v>
       </c>
       <c r="E16" t="n">
-        <v>0.117</v>
+        <v>-0.0824</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1218</v>
+        <v>1.366</v>
       </c>
       <c r="G16" t="n">
         <v>1.059</v>
@@ -1702,13 +1702,13 @@
         <v>1.9474</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.235</v>
+        <v>-0.1901</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2501</v>
+        <v>0.0508</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4851</v>
+        <v>-0.2409</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5590000000000001</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7652</v>
+        <v>0.0577</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.1568</v>
+        <v>0.0294</v>
       </c>
       <c r="F17" t="n">
-        <v>3.922</v>
+        <v>0.0283</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8637</v>
+        <v>0.4929</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.2711</v>
+        <v>0.1621</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1348</v>
+        <v>0.3308</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4372</v>
+        <v>0.106</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.3186</v>
+        <v>0.0411</v>
       </c>
       <c r="L17" t="n">
-        <v>2.7558</v>
+        <v>0.065</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5735</v>
+        <v>0.3869</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9525</v>
+        <v>0.1211</v>
       </c>
       <c r="O17" t="n">
-        <v>0.379</v>
+        <v>0.2658</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3632</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8947</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5316</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2647</v>
+        <v>0.2017</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3682</v>
+        <v>-0.0766</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6329</v>
+        <v>0.2783</v>
       </c>
       <c r="V17" t="n">
+        <v>-1.2211</v>
+      </c>
+      <c r="W17" t="n">
         <v>0</v>
       </c>
-      <c r="W17" t="n">
-        <v>-0.3311</v>
-      </c>
       <c r="X17" t="n">
-        <v>0.3311</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3418</v>
+        <v>-0.1647</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0703</v>
+        <v>-3.0571</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2716</v>
+        <v>2.8924</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4929</v>
+        <v>0.8637</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1621</v>
+        <v>-2.2711</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3308</v>
+        <v>3.1348</v>
       </c>
       <c r="J18" t="n">
-        <v>0.106</v>
+        <v>1.4372</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0411</v>
+        <v>-1.3186</v>
       </c>
       <c r="L18" t="n">
-        <v>0.065</v>
+        <v>2.7558</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3869</v>
+        <v>-0.5735</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1211</v>
+        <v>-0.9525</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2658</v>
+        <v>0.379</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5842000000000001</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q18" t="n">
+        <v>-3.8947</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.5316</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.2685</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.6032999999999999</v>
+      </c>
+      <c r="V18" t="n">
         <v>0</v>
       </c>
-      <c r="R18" t="n">
-        <v>0.5842000000000001</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-0.1979</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-0.1763</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-0.0216</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-1.2211</v>
-      </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.3311</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2211</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5583</v>
+        <v>-0.3535</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3052</v>
+        <v>-2.2056</v>
       </c>
       <c r="F19" t="n">
-        <v>1.747</v>
+        <v>1.852</v>
       </c>
       <c r="G19" t="n">
         <v>0.4408</v>
@@ -1936,13 +1936,13 @@
         <v>1.1684</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6028</v>
+        <v>-0.398</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4236</v>
+        <v>-0.3239</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1791</v>
+        <v>-0.0741</v>
       </c>
       <c r="V19" t="n">
         <v>0.3826</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1084</v>
+        <v>-0.6586</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3767</v>
+        <v>-2.1774</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2683</v>
+        <v>1.5187</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0451</v>
@@ -2014,13 +2014,13 @@
         <v>1.3632</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0633</v>
+        <v>-0.6135</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3525</v>
+        <v>-0.1532</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7108</v>
+        <v>-0.4603</v>
       </c>
       <c r="V20" t="n">
         <v>0.6105</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1463</v>
+        <v>-0.8797</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.459</v>
+        <v>-1.3593</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3126</v>
+        <v>0.4796</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4971</v>
@@ -2092,13 +2092,13 @@
         <v>0.7789</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4544</v>
+        <v>-0.1878</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4947</v>
+        <v>-0.395</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0402</v>
+        <v>0.2072</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2278</v>
+        <v>-2.2369</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4173</v>
+        <v>-2.816</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1895</v>
+        <v>0.579</v>
       </c>
       <c r="G22" t="n">
         <v>1.0379</v>
@@ -2170,13 +2170,13 @@
         <v>2.921</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7915</v>
+        <v>-0.8006</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0129</v>
+        <v>-0.4116</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7786</v>
+        <v>-0.389</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5005</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>9.4923</v>
+        <v>10.1568</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1974</v>
+        <v>1.197299999999998</v>
       </c>
       <c r="F23" t="n">
-        <v>8.2948</v>
+        <v>8.959200000000001</v>
       </c>
       <c r="G23" t="n">
         <v>8.3881</v>
@@ -2248,13 +2248,13 @@
         <v>18.4999</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.2764</v>
+        <v>-2.6118</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.6303</v>
+        <v>-2.6301</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6462</v>
+        <v>0.01829999999999998</v>
       </c>
       <c r="V23" t="n">
         <v>0.4857</v>
